--- a/Result/profitability/2495.xlsx
+++ b/Result/profitability/2495.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4687500000000001</v>
+        <v>0.4187500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>46.585</v>
+        <v>45.79</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>0.47875</v>
+        <v>0.44875</v>
       </c>
       <c r="N3" t="n">
-        <v>47.72</v>
+        <v>46.98375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5287500000000001</v>
+        <v>0.52375</v>
       </c>
       <c r="N4" t="n">
-        <v>48.35375000000001</v>
+        <v>48.0325</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.65625</v>
+        <v>0.76875</v>
       </c>
       <c r="N5" t="n">
-        <v>50.07</v>
+        <v>50.01375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.85875</v>
+        <v>0.80125</v>
       </c>
       <c r="N6" t="n">
-        <v>52.4825</v>
+        <v>52.9575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0.81875</v>
+        <v>0.76875</v>
       </c>
       <c r="N7" t="n">
-        <v>55.2725</v>
+        <v>55.27375000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.79</v>
+        <v>0.7837500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>57.47000000000001</v>
+        <v>57.90875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.46</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7875</v>
+        <v>0.7875000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>60.13</v>
@@ -1772,10 +1772,10 @@
         <v>0.37</v>
       </c>
       <c r="M11" t="n">
-        <v>0.73875</v>
+        <v>0.7387500000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>60.06875</v>
+        <v>60.06874999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>409</v>
+      </c>
+      <c r="D75" t="n">
+        <v>232</v>
+      </c>
+      <c r="E75" t="n">
+        <v>177</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>64</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>21</v>
+      </c>
+      <c r="J75" t="n">
+        <v>85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>75</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3662500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>44.31375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1515151515151515</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.509999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08816880180859066</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.451612903225806</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4500000000000028</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01028101439342022</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
